--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -1,55 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E9EF06-7AF5-4CD2-B054-546477608C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Air Cairo Flight</t>
+  </si>
+  <si>
+    <t>Market Threat Airline</t>
+  </si>
+  <si>
+    <t>OAL Fare Threat</t>
+  </si>
+  <si>
+    <t>Our Fare</t>
+  </si>
+  <si>
+    <t>Fare Dif</t>
+  </si>
+  <si>
+    <t>OAL Baggage</t>
+  </si>
+  <si>
+    <t>Our Baggage</t>
+  </si>
+  <si>
+    <t>Bag Allowance Dif</t>
+  </si>
+  <si>
+    <t>IMPACT</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>01-JAN-26</t>
+  </si>
+  <si>
+    <t>SM-321</t>
+  </si>
+  <si>
+    <t>Nile Air NP-119</t>
+  </si>
+  <si>
+    <t>LOW THREAT</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003498DB"/>
-        <bgColor rgb="003498DB"/>
+        <fgColor rgb="FF3498DB"/>
+        <bgColor rgb="FF3498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,99 +128,49 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -442,127 +458,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="153.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Air Cairo Flight</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Market Threat Airline</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Fare Threat</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Our Fare</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fare Dif</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Baggage</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Our Baggage</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Bag Allowance Dif</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>IMPACT</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>01-JAN-26</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2">
         <v>6009</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>6364</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>-355</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -1,121 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E9EF06-7AF5-4CD2-B054-546477608C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Air Cairo Flight</t>
-  </si>
-  <si>
-    <t>Market Threat Airline</t>
-  </si>
-  <si>
-    <t>OAL Fare Threat</t>
-  </si>
-  <si>
-    <t>Our Fare</t>
-  </si>
-  <si>
-    <t>Fare Dif</t>
-  </si>
-  <si>
-    <t>OAL Baggage</t>
-  </si>
-  <si>
-    <t>Our Baggage</t>
-  </si>
-  <si>
-    <t>Bag Allowance Dif</t>
-  </si>
-  <si>
-    <t>IMPACT</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>01-JAN-26</t>
-  </si>
-  <si>
-    <t>SM-321</t>
-  </si>
-  <si>
-    <t>Nile Air NP-119</t>
-  </si>
-  <si>
-    <t>LOW THREAT</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3498DB"/>
-        <bgColor rgb="FF3498DB"/>
+        <fgColor rgb="003498DB"/>
+        <bgColor rgb="003498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,49 +62,99 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,91 +442,262 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="153.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Air Cairo Flight</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Market Threat Airline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Fare Threat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Our Fare</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fare Dif</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Baggage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Our Baggage</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bag Allowance Dif</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IMPACT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>01-JAN-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6009</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6364</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>-355</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2">
-        <v>6009</v>
-      </c>
-      <c r="E2" s="2">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>05-FEB-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6339</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>6364</v>
       </c>
-      <c r="F2" s="2">
-        <v>-355</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F3" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>12-FEB-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6339</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7378</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-1039</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>19-FEB-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6339</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7378</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-1039</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -1,55 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E9EF06-7AF5-4CD2-B054-546477608C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Air Cairo Flight</t>
+  </si>
+  <si>
+    <t>Market Threat Airline</t>
+  </si>
+  <si>
+    <t>OAL Fare Threat</t>
+  </si>
+  <si>
+    <t>Our Fare</t>
+  </si>
+  <si>
+    <t>Fare Dif</t>
+  </si>
+  <si>
+    <t>OAL Baggage</t>
+  </si>
+  <si>
+    <t>Our Baggage</t>
+  </si>
+  <si>
+    <t>Bag Allowance Dif</t>
+  </si>
+  <si>
+    <t>IMPACT</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>01-JAN-26</t>
+  </si>
+  <si>
+    <t>SM-321</t>
+  </si>
+  <si>
+    <t>Nile Air NP-119</t>
+  </si>
+  <si>
+    <t>LOW THREAT</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003498DB"/>
-        <bgColor rgb="003498DB"/>
+        <fgColor rgb="FF3498DB"/>
+        <bgColor rgb="FF3498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,99 +128,49 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -442,262 +458,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="153.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Air Cairo Flight</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Market Threat Airline</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Fare Threat</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Our Fare</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fare Dif</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Baggage</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Our Baggage</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Bag Allowance Dif</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>IMPACT</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>01-JAN-26</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2">
         <v>6009</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>6364</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>-355</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>05-FEB-26</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>6339</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6364</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>12-FEB-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6339</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>7378</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-1039</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>19-FEB-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>6339</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>7378</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-1039</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -1,121 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E9EF06-7AF5-4CD2-B054-546477608C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Air Cairo Flight</t>
-  </si>
-  <si>
-    <t>Market Threat Airline</t>
-  </si>
-  <si>
-    <t>OAL Fare Threat</t>
-  </si>
-  <si>
-    <t>Our Fare</t>
-  </si>
-  <si>
-    <t>Fare Dif</t>
-  </si>
-  <si>
-    <t>OAL Baggage</t>
-  </si>
-  <si>
-    <t>Our Baggage</t>
-  </si>
-  <si>
-    <t>Bag Allowance Dif</t>
-  </si>
-  <si>
-    <t>IMPACT</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>01-JAN-26</t>
-  </si>
-  <si>
-    <t>SM-321</t>
-  </si>
-  <si>
-    <t>Nile Air NP-119</t>
-  </si>
-  <si>
-    <t>LOW THREAT</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3498DB"/>
-        <bgColor rgb="FF3498DB"/>
+        <fgColor rgb="003498DB"/>
+        <bgColor rgb="003498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,49 +68,102 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,91 +451,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="153.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Air Cairo Flight</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Market Threat Airline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Fare Threat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Our Fare</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fare Dif</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Baggage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Our Baggage</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bag Allowance Dif</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IMPACT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>01-JAN-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6039</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6396</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>-357</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2">
-        <v>6009</v>
-      </c>
-      <c r="E2" s="2">
-        <v>6364</v>
-      </c>
-      <c r="F2" s="2">
-        <v>-355</v>
-      </c>
-      <c r="G2" s="2">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>08-JAN-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6371</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6396</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>05-FEB-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6371</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6396</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>12-FEB-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6371</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7416</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-1045</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>19-FEB-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6371</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>7416</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-1045</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>26-MAR-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>14016</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>17062</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-3046</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-FEB-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6005</v>
+        <v>17272</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6018</v>
+        <v>19326</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-13</v>
+        <v>-2054</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6005</v>
+        <v>14295</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6018</v>
+        <v>14750</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-13</v>
+        <v>-455</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>04-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-209</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6005</v>
+        <v>10669</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6018</v>
+        <v>11221</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-13</v>
+        <v>-552</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13937</v>
+        <v>7347</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18828</v>
+        <v>7402</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4891</v>
+        <v>-55</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,12 +689,417 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>09-APR-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6740</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-193</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>11-APR-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-209</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6740</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6823</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-83</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>18-APR-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-209</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>23-APR-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6933</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17272</v>
+        <v>10830</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19326</v>
+        <v>11630</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2054</v>
+        <v>-800</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14295</v>
+        <v>10830</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14750</v>
+        <v>11630</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-455</v>
+        <v>-800</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10669</v>
+        <v>7701</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11221</v>
+        <v>7940</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-552</v>
+        <v>-239</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,17 +668,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7347</v>
+        <v>7701</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7402</v>
+        <v>7940</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-55</v>
+        <v>-239</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>18-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-209</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6740</v>
+        <v>6748</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6933</v>
+        <v>6790</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-193</v>
+        <v>-42</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>18-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6740</v>
+        <v>6748</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6823</v>
+        <v>6790</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-83</v>
+        <v>-42</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6382</v>
+        <v>7926</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6933</v>
+        <v>8347</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-551</v>
+        <v>-421</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6382</v>
+        <v>7926</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6933</v>
+        <v>8347</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-551</v>
+        <v>-421</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6382</v>
+        <v>10830</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6933</v>
+        <v>13004</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-551</v>
+        <v>-2174</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6382</v>
+        <v>10830</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6933</v>
+        <v>13004</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-551</v>
+        <v>-2174</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6382</v>
+        <v>10830</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6933</v>
+        <v>13004</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-551</v>
+        <v>-2174</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6382</v>
+        <v>10830</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6933</v>
+        <v>13004</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-551</v>
+        <v>-2174</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6382</v>
+        <v>10830</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6933</v>
+        <v>13004</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-551</v>
+        <v>-2174</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1100,6 +1100,411 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10830</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>13004</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-2174</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-337</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-337</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>7940</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-491</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>7940</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-491</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>24-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-337</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>24-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>7786</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-337</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>7940</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-491</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7449</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>7940</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-491</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10830</v>
+        <v>6763</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11630</v>
+        <v>7341</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-800</v>
+        <v>-578</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10830</v>
+        <v>7242</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11630</v>
+        <v>7341</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-800</v>
+        <v>-99</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7701</v>
+        <v>6763</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7940</v>
+        <v>7341</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-239</v>
+        <v>-578</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,27 +676,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-321</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7701</v>
+        <v>7242</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7940</v>
+        <v>7341</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-239</v>
+        <v>-99</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6748</v>
+        <v>9525</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6790</v>
+        <v>15767</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-42</v>
+        <v>-6242</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -734,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -748,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6748</v>
+        <v>7467</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6790</v>
+        <v>7538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-42</v>
+        <v>-71</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7926</v>
+        <v>7467</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8347</v>
+        <v>7538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-421</v>
+        <v>-71</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7926</v>
+        <v>7721</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8347</v>
+        <v>7735</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-421</v>
+        <v>-14</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10830</v>
+        <v>7721</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2174</v>
+        <v>-14</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10830</v>
+        <v>7467</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2174</v>
+        <v>-268</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10830</v>
+        <v>7467</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2174</v>
+        <v>-268</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1032,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10830</v>
+        <v>8679</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13004</v>
+        <v>9708</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2174</v>
+        <v>-1029</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1077,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10830</v>
+        <v>8679</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13004</v>
+        <v>9708</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2174</v>
+        <v>-1029</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1108,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10830</v>
+        <v>10835</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13004</v>
+        <v>12188</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2174</v>
+        <v>-1353</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1153,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1167,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7449</v>
+        <v>10835</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-337</v>
+        <v>-2733</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7449</v>
+        <v>10835</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-337</v>
+        <v>-2733</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1253,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7449</v>
+        <v>9525</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7940</v>
+        <v>12188</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-491</v>
+        <v>-2663</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1302,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7449</v>
+        <v>9525</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7940</v>
+        <v>11314</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-491</v>
+        <v>-1789</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1333,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1347,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7449</v>
+        <v>8679</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-337</v>
+        <v>-4889</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1364,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1378,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1392,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7449</v>
+        <v>8679</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-337</v>
+        <v>-4889</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1409,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1423,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1437,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7449</v>
+        <v>7721</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7940</v>
+        <v>13568</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-491</v>
+        <v>-5847</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1454,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1468,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1478,33 +1496,213 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>13568</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-6101</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-109</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>7449</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>7940</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-491</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>13568</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-6101</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-874</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-874</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>8482</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-321</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6763</v>
+        <v>7242</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>7341</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-578</v>
+        <v>-99</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,12 +676,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-973</t>
+          <t>SM-321</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7242</v>
+        <v>9525</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7341</v>
+        <v>15767</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-99</v>
+        <v>-6242</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9525</v>
+        <v>10835</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15767</v>
+        <v>11314</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6242</v>
+        <v>-479</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7467</v>
+        <v>7721</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7538</v>
+        <v>7735</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-71</v>
+        <v>-14</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7467</v>
+        <v>7721</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7538</v>
+        <v>7735</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-71</v>
+        <v>-14</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7721</v>
+        <v>7467</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>7735</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-14</v>
+        <v>-268</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7721</v>
+        <v>7467</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>7735</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>-268</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7467</v>
+        <v>8679</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7735</v>
+        <v>9708</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-268</v>
+        <v>-1029</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7467</v>
+        <v>8679</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7735</v>
+        <v>9708</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-268</v>
+        <v>-1029</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8679</v>
+        <v>10835</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9708</v>
+        <v>13568</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1029</v>
+        <v>-2733</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8679</v>
+        <v>10835</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9708</v>
+        <v>13568</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1029</v>
+        <v>-2733</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
         <v>10835</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12188</v>
+        <v>13568</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1353</v>
+        <v>-2733</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10835</v>
+        <v>9525</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13568</v>
+        <v>12188</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2733</v>
+        <v>-2663</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10835</v>
+        <v>9525</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13568</v>
+        <v>12188</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2733</v>
+        <v>-2663</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9525</v>
+        <v>8679</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12188</v>
+        <v>13568</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2663</v>
+        <v>-4889</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9525</v>
+        <v>8679</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11314</v>
+        <v>13568</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1789</v>
+        <v>-4889</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8679</v>
+        <v>7721</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>13568</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4889</v>
+        <v>-5847</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8679</v>
+        <v>7467</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>13568</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4889</v>
+        <v>-6101</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7721</v>
+        <v>7467</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>13568</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5847</v>
+        <v>-6101</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1503,10 +1503,10 @@
         <v>7467</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13568</v>
+        <v>8341</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-6101</v>
+        <v>-874</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1548,10 +1548,10 @@
         <v>7467</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13568</v>
+        <v>8341</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-6101</v>
+        <v>-874</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1593,10 +1593,10 @@
         <v>7467</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8341</v>
+        <v>8482</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-874</v>
+        <v>-1015</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1613,96 +1613,6 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>7467</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>8341</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-874</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>7467</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>8482</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-1015</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -48,12 +48,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
       </patternFill>
@@ -62,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6763</v>
+        <v>9427</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7341</v>
+        <v>16553</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-578</v>
+        <v>-7126</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7242</v>
+        <v>10724</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7341</v>
+        <v>14084</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-99</v>
+        <v>-3360</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-973</t>
+          <t>SM-321</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7242</v>
+        <v>10724</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7341</v>
+        <v>12104</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-99</v>
+        <v>-1380</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9525</v>
+        <v>9427</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15767</v>
+        <v>11114</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6242</v>
+        <v>-1687</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10835</v>
+        <v>9427</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11314</v>
+        <v>10124</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-479</v>
+        <v>-697</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7721</v>
+        <v>8339</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7735</v>
+        <v>9134</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-14</v>
+        <v>-795</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7721</v>
+        <v>8339</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7735</v>
+        <v>9134</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-14</v>
+        <v>-795</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7467</v>
+        <v>8590</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7735</v>
+        <v>14084</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-268</v>
+        <v>-5494</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7467</v>
+        <v>8590</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7735</v>
+        <v>13094</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-268</v>
+        <v>-4504</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8679</v>
+        <v>10724</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9708</v>
+        <v>16553</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1029</v>
+        <v>-5829</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8679</v>
+        <v>14349</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9708</v>
+        <v>18533</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1029</v>
+        <v>-4184</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10835</v>
+        <v>10724</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2733</v>
+        <v>-5829</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10835</v>
+        <v>10724</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2733</v>
+        <v>-5829</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10835</v>
+        <v>9427</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13568</v>
+        <v>15075</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2733</v>
+        <v>-5648</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9525</v>
+        <v>9427</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12188</v>
+        <v>15075</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2663</v>
+        <v>-5648</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9525</v>
+        <v>8590</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12188</v>
+        <v>16553</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2663</v>
+        <v>-7963</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8679</v>
+        <v>8590</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4889</v>
+        <v>-7963</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8679</v>
+        <v>7391</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4889</v>
+        <v>-9162</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7721</v>
+        <v>7391</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-5847</v>
+        <v>-9162</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13568</v>
+        <v>16553</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-6101</v>
+        <v>-9162</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13568</v>
+        <v>9134</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-6101</v>
+        <v>-1743</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8341</v>
+        <v>9134</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-874</v>
+        <v>-1743</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8341</v>
+        <v>10124</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-874</v>
+        <v>-2733</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,57 +1562,12 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>7467</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>8482</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-1015</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9427</v>
+        <v>4894</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16553</v>
+        <v>4908</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7126</v>
+        <v>-14</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-321</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10724</v>
+        <v>4894</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14084</v>
+        <v>4908</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3360</v>
+        <v>-14</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>10724</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12104</v>
+        <v>14043</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1380</v>
+        <v>-3319</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9427</v>
+        <v>10724</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11114</v>
+        <v>11100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1687</v>
+        <v>-376</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9427</v>
+        <v>9399</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10124</v>
+        <v>10110</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-697</v>
+        <v>-711</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8339</v>
+        <v>7614</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9134</v>
+        <v>7642</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-795</v>
+        <v>-28</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>8339</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9134</v>
+        <v>9120</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-795</v>
+        <v>-781</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8590</v>
+        <v>8339</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14084</v>
+        <v>9120</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5494</v>
+        <v>-781</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8590</v>
+        <v>8562</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13094</v>
+        <v>14043</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4504</v>
+        <v>-5481</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10724</v>
+        <v>8562</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16553</v>
+        <v>14043</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5829</v>
+        <v>-5481</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14349</v>
+        <v>10724</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18533</v>
+        <v>16511</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4184</v>
+        <v>-5787</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10724</v>
+        <v>14294</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16553</v>
+        <v>20444</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5829</v>
+        <v>-6150</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>10724</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5829</v>
+        <v>-5787</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9427</v>
+        <v>10724</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15075</v>
+        <v>16511</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5648</v>
+        <v>-5787</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9427</v>
+        <v>9399</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15075</v>
+        <v>15033</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-5648</v>
+        <v>-5634</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8590</v>
+        <v>8562</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-7963</v>
+        <v>-7949</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8590</v>
+        <v>8562</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-7963</v>
+        <v>-7949</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1323,10 +1323,10 @@
         <v>7391</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-9162</v>
+        <v>-9120</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1368,10 +1368,10 @@
         <v>7391</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-9162</v>
+        <v>-9120</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1413,10 +1413,10 @@
         <v>7391</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16553</v>
+        <v>16511</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-9162</v>
+        <v>-9120</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         <v>7391</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9134</v>
+        <v>9120</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1743</v>
+        <v>-1729</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1503,10 +1503,10 @@
         <v>7391</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9134</v>
+        <v>9120</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1743</v>
+        <v>-1729</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1548,10 +1548,10 @@
         <v>7391</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10124</v>
+        <v>10110</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2733</v>
+        <v>-2719</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -700,96 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>9541</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>10248</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-707</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>8691</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9257</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-566</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,10 +555,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4968</v>
+        <v>4946</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4982</v>
+        <v>4960</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>-14</v>
@@ -582,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7502</v>
+        <v>7469</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7757</v>
+        <v>7736</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-255</v>
+        <v>-267</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -627,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14481</v>
+        <v>14473</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15245</v>
+        <v>15219</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-764</v>
+        <v>-746</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -672,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10857</v>
+        <v>10837</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11253</v>
+        <v>11231</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-396</v>
+        <v>-394</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -695,6 +713,861 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9498</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-733</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7722</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>7736</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9230</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-549</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-5538</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>13232</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-4551</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>17643</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>20716</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-3073</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>19-AUG-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>14473</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-2254</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>14473</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-2254</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>26-AUG-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10837</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>15219</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-4382</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>9498</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>15219</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-5721</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-8046</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-8046</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>8681</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-8046</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-9258</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-9258</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>16727</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-9258</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>9230</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-1761</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>9230</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-1761</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>10231</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-2762</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -648,10 +648,10 @@
         <v>14473</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15219</v>
+        <v>15234</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-746</v>
+        <v>-761</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>10837</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11231</v>
+        <v>13232</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-394</v>
+        <v>-2395</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9498</v>
+        <v>10837</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10231</v>
+        <v>11231</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-733</v>
+        <v>-394</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7722</v>
+        <v>9526</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7736</v>
+        <v>11231</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-14</v>
+        <v>-1705</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8681</v>
+        <v>7722</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14219</v>
+        <v>7736</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5538</v>
+        <v>-14</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>8681</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13232</v>
+        <v>9230</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4551</v>
+        <v>-549</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17643</v>
+        <v>8681</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>20716</v>
+        <v>14233</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3073</v>
+        <v>-5552</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14473</v>
+        <v>8681</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16727</v>
+        <v>14233</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2254</v>
+        <v>-5552</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14473</v>
+        <v>17672</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16727</v>
+        <v>20730</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2254</v>
+        <v>-3058</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10837</v>
+        <v>14473</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15219</v>
+        <v>16727</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4382</v>
+        <v>-2254</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9498</v>
+        <v>14473</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15219</v>
+        <v>16727</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5721</v>
+        <v>-2254</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8681</v>
+        <v>10837</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16727</v>
+        <v>15234</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-8046</v>
+        <v>-4397</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8681</v>
+        <v>9526</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16727</v>
+        <v>15234</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-8046</v>
+        <v>-5708</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7469</v>
+        <v>8681</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>16727</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-9258</v>
+        <v>-8046</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7469</v>
+        <v>8681</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>16727</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-9258</v>
+        <v>-8046</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         <v>7469</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9230</v>
+        <v>16727</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1761</v>
+        <v>-9258</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1503,10 +1503,10 @@
         <v>7469</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9230</v>
+        <v>16727</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1761</v>
+        <v>-9258</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>30-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1548,26 +1548,116 @@
         <v>7469</v>
       </c>
       <c r="E24" s="2" t="n">
+        <v>9230</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-1761</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>9230</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-1761</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7469</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>10231</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>-2762</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -693,10 +693,10 @@
         <v>10837</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13232</v>
+        <v>14233</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2395</v>
+        <v>-3396</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-973</t>
+          <t>SM-321</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4946</v>
+        <v>10834</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4960</v>
+        <v>13207</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-14</v>
+        <v>-2373</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7469</v>
+        <v>8642</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7736</v>
+        <v>9200</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-267</v>
+        <v>-558</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14473</v>
+        <v>8642</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15234</v>
+        <v>9200</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-761</v>
+        <v>-558</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10837</v>
+        <v>8642</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14233</v>
+        <v>14212</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3396</v>
+        <v>-5570</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10837</v>
+        <v>9479</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11231</v>
+        <v>14212</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-394</v>
+        <v>-4733</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9526</v>
+        <v>17661</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11231</v>
+        <v>18722</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1705</v>
+        <v>-1061</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8681</v>
+        <v>17661</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9230</v>
+        <v>20718</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-549</v>
+        <v>-3057</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7722</v>
+        <v>14478</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7736</v>
+        <v>16711</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-14</v>
+        <v>-2233</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8681</v>
+        <v>14478</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9230</v>
+        <v>16711</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-549</v>
+        <v>-2233</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8681</v>
+        <v>10834</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14233</v>
+        <v>15218</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5552</v>
+        <v>-4384</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8681</v>
+        <v>9479</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14233</v>
+        <v>15218</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5552</v>
+        <v>-5739</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>17672</v>
+        <v>8642</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20730</v>
+        <v>16711</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3058</v>
+        <v>-8069</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14473</v>
+        <v>9479</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16727</v>
+        <v>16711</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2254</v>
+        <v>-7232</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14473</v>
+        <v>8642</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16727</v>
+        <v>16711</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2254</v>
+        <v>-8069</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10837</v>
+        <v>7441</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>15234</v>
+        <v>16711</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4397</v>
+        <v>-9270</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9526</v>
+        <v>7441</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15234</v>
+        <v>16711</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5708</v>
+        <v>-9270</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8681</v>
+        <v>7441</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16727</v>
+        <v>16711</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-8046</v>
+        <v>-9270</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8681</v>
+        <v>7441</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16727</v>
+        <v>9200</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-8046</v>
+        <v>-1759</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8681</v>
+        <v>7441</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16727</v>
+        <v>9200</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-8046</v>
+        <v>-1759</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7469</v>
+        <v>7441</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16727</v>
+        <v>10205</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-9258</v>
+        <v>-2764</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,237 +1427,12 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>7469</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>16727</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-9258</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>7469</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>16727</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-9258</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>7469</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>9230</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-1761</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>7469</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>9230</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-1761</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>7469</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>10231</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-2762</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AJF_threats.xlsx
+++ b/excel_routes/route_CAI_AJF_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10834</v>
+        <v>10736</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13207</v>
+        <v>11095</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2373</v>
+        <v>-359</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8642</v>
+        <v>8570</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9200</v>
+        <v>14090</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-558</v>
+        <v>-5520</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8642</v>
+        <v>9398</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9200</v>
+        <v>14090</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-558</v>
+        <v>-4692</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8642</v>
+        <v>17457</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14212</v>
+        <v>18561</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5570</v>
+        <v>-1104</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9479</v>
+        <v>17457</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14212</v>
+        <v>20562</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4733</v>
+        <v>-3105</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17661</v>
+        <v>14366</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18722</v>
+        <v>16574</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1061</v>
+        <v>-2208</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17661</v>
+        <v>14366</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20718</v>
+        <v>16574</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3057</v>
+        <v>-2208</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14478</v>
+        <v>10736</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16711</v>
+        <v>15083</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2233</v>
+        <v>-4347</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14478</v>
+        <v>9398</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16711</v>
+        <v>15083</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2233</v>
+        <v>-5685</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10834</v>
+        <v>8570</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15218</v>
+        <v>16574</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4384</v>
+        <v>-8004</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9479</v>
+        <v>9398</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15218</v>
+        <v>16574</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5739</v>
+        <v>-7176</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8642</v>
+        <v>8570</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16711</v>
+        <v>16574</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-8069</v>
+        <v>-8004</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9479</v>
+        <v>7603</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16711</v>
+        <v>16574</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-7232</v>
+        <v>-8971</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8642</v>
+        <v>7355</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16711</v>
+        <v>16574</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-8069</v>
+        <v>-9219</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7441</v>
+        <v>7355</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16711</v>
+        <v>16574</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-9270</v>
+        <v>-9219</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7441</v>
+        <v>7355</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16711</v>
+        <v>9108</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-9270</v>
+        <v>-1753</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1247,192 +1247,12 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>7441</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>16711</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-9270</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>7441</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-1759</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>7441</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-1759</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>7441</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>10205</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-2764</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
